--- a/research/traditional_assets/database/data/egypt/egypt_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.257</v>
+        <v>0.109</v>
       </c>
       <c r="E2">
-        <v>0.415</v>
+        <v>0.0491</v>
       </c>
       <c r="G2">
-        <v>0.2593320235756384</v>
+        <v>0.2548421052631579</v>
       </c>
       <c r="H2">
-        <v>0.2593320235756384</v>
+        <v>0.2548421052631579</v>
       </c>
       <c r="I2">
-        <v>0.2601178781925343</v>
+        <v>0.241578947368421</v>
       </c>
       <c r="J2">
-        <v>0.2372541384756298</v>
+        <v>0.2008041315757994</v>
       </c>
       <c r="K2">
-        <v>24.42</v>
+        <v>19.69</v>
       </c>
       <c r="L2">
-        <v>0.2398821218074656</v>
+        <v>0.2072631578947368</v>
       </c>
       <c r="M2">
-        <v>2.06</v>
+        <v>6.28</v>
       </c>
       <c r="N2">
-        <v>0.01201866977829638</v>
+        <v>0.06162904808635918</v>
       </c>
       <c r="O2">
-        <v>0.08435708435708435</v>
+        <v>0.318943626206196</v>
       </c>
       <c r="P2">
-        <v>2.06</v>
+        <v>6.28</v>
       </c>
       <c r="Q2">
-        <v>0.01201866977829638</v>
+        <v>0.06162904808635918</v>
       </c>
       <c r="R2">
-        <v>0.08435708435708435</v>
+        <v>0.318943626206196</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,19 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>20.38</v>
+        <v>10.4</v>
       </c>
       <c r="V2">
-        <v>0.1189031505250875</v>
-      </c>
-      <c r="W2">
-        <v>0.3082336355012122</v>
+        <v>0.1020608439646712</v>
       </c>
       <c r="X2">
-        <v>0.08288873247043339</v>
-      </c>
-      <c r="Y2">
-        <v>0.2253449030307788</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="Z2">
-        <v>1.579249468670979</v>
-      </c>
-      <c r="AA2">
-        <v>0.3656198871487573</v>
+        <v>2.553763440860215</v>
       </c>
       <c r="AB2">
-        <v>0.08288873247043339</v>
-      </c>
-      <c r="AC2">
-        <v>0.2827311546783239</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-20.38</v>
+        <v>-10.4</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,28 +669,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.1349490133757119</v>
+        <v>-0.1136612021857924</v>
       </c>
       <c r="AK2">
-        <v>-0.2698622881355932</v>
+        <v>-0.2561576354679803</v>
       </c>
       <c r="AL2">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="AM2">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>441.3333333333333</v>
+        <v>388.9830508474577</v>
       </c>
       <c r="AP2">
-        <v>-0.7593144560357675</v>
+        <v>-0.4461604461604461</v>
       </c>
       <c r="AQ2">
-        <v>441.3333333333333</v>
+        <v>388.9830508474577</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Delta Insurance Company (CASE:DEIN)</t>
+          <t>Mohandes Insurance Company (CASE:MOIN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +710,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.257</v>
+        <v>0.109</v>
       </c>
       <c r="E3">
-        <v>0.415</v>
+        <v>0.0491</v>
       </c>
       <c r="G3">
-        <v>0.2562893081761006</v>
+        <v>0.2143631436314363</v>
       </c>
       <c r="H3">
-        <v>0.2562893081761006</v>
+        <v>0.2143631436314363</v>
       </c>
       <c r="I3">
-        <v>0.2657232704402516</v>
+        <v>0.2100271002710027</v>
       </c>
       <c r="J3">
-        <v>0.2282804459691252</v>
+        <v>0.173681248555378</v>
       </c>
       <c r="K3">
-        <v>15.1</v>
+        <v>6.69</v>
       </c>
       <c r="L3">
-        <v>0.2374213836477987</v>
+        <v>0.1813008130081301</v>
       </c>
       <c r="M3">
-        <v>2.06</v>
+        <v>2.91</v>
       </c>
       <c r="N3">
-        <v>0.02273730684326711</v>
+        <v>0.05553435114503817</v>
       </c>
       <c r="O3">
-        <v>0.1364238410596026</v>
+        <v>0.4349775784753363</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.91</v>
       </c>
       <c r="Q3">
-        <v>0.02273730684326711</v>
+        <v>0.05553435114503817</v>
       </c>
       <c r="R3">
-        <v>0.1364238410596026</v>
+        <v>0.4349775784753363</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +758,16 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.1589403973509934</v>
-      </c>
-      <c r="W3">
-        <v>0.3561320754716981</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.08288873247043339</v>
-      </c>
-      <c r="Y3">
-        <v>0.2732433430012647</v>
-      </c>
-      <c r="Z3">
-        <v>1.884444444444445</v>
-      </c>
-      <c r="AA3">
-        <v>0.4301818181818182</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AB3">
-        <v>0.08288873247043339</v>
-      </c>
-      <c r="AC3">
-        <v>0.3472930857113848</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,31 +779,31 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-14.4</v>
+        <v>0</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
       <c r="AJ3">
-        <v>-0.1889763779527559</v>
-      </c>
-      <c r="AK3">
-        <v>-0.3645569620253165</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>131.3559322033898</v>
+      </c>
       <c r="AP3">
-        <v>-0.8421052631578947</v>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>131.3559322033898</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +814,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mohandes Insurance Company (CASE:MOIN)</t>
+          <t>Delta Insurance Company (CASE:DEIN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,70 +823,73 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.2643979057591623</v>
+        <v>0.2805507745266781</v>
       </c>
       <c r="H4">
-        <v>0.2643979057591623</v>
+        <v>0.2805507745266781</v>
       </c>
       <c r="I4">
-        <v>0.2507853403141361</v>
+        <v>0.261617900172117</v>
       </c>
       <c r="J4">
-        <v>0.2420364107400302</v>
+        <v>0.2185775359502526</v>
       </c>
       <c r="K4">
-        <v>9.32</v>
+        <v>13</v>
       </c>
       <c r="L4">
-        <v>0.243979057591623</v>
+        <v>0.2237521514629948</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>3.37</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.06808080808080809</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2592307692307693</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>3.37</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.06808080808080809</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2592307692307693</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>5.98</v>
+        <v>10.4</v>
       </c>
       <c r="V4">
-        <v>0.07400990099009902</v>
+        <v>0.2101010101010101</v>
       </c>
       <c r="W4">
-        <v>0.2603351955307263</v>
+        <v>0.2490421455938697</v>
       </c>
       <c r="X4">
-        <v>0.08288873247043339</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="Y4">
-        <v>0.1774464630602929</v>
+        <v>0.115948508359119</v>
       </c>
       <c r="Z4">
-        <v>1.243853993683045</v>
+        <v>1.561827956989247</v>
       </c>
       <c r="AA4">
-        <v>0.3010579561156964</v>
+        <v>0.3413805064169267</v>
       </c>
       <c r="AB4">
-        <v>0.08288873247043339</v>
+        <v>0.1330936372347507</v>
       </c>
       <c r="AC4">
-        <v>0.218169223645263</v>
+        <v>0.208286869182176</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -925,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-5.98</v>
+        <v>-10.4</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -934,28 +910,22 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.07992515370221867</v>
+        <v>-0.2659846547314578</v>
       </c>
       <c r="AK4">
-        <v>-0.1660188784008884</v>
+        <v>-0.2561576354679803</v>
       </c>
       <c r="AL4">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
-      <c r="AO4">
-        <v>159.6666666666667</v>
-      </c>
       <c r="AP4">
-        <v>-0.6139630390143738</v>
-      </c>
-      <c r="AQ4">
-        <v>159.6666666666667</v>
+        <v>-0.6753246753246753</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/egypt/egypt_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.109</v>
+        <v>0.143</v>
       </c>
       <c r="E2">
-        <v>0.0491</v>
+        <v>0.101</v>
       </c>
       <c r="G2">
-        <v>0.2548421052631579</v>
+        <v>0.2841965471447542</v>
       </c>
       <c r="H2">
-        <v>0.2548421052631579</v>
+        <v>0.2841965471447542</v>
       </c>
       <c r="I2">
-        <v>0.241578947368421</v>
+        <v>0.2710491367861885</v>
       </c>
       <c r="J2">
-        <v>0.2008041315757994</v>
+        <v>0.2153482509191402</v>
       </c>
       <c r="K2">
-        <v>19.69</v>
+        <v>18.79</v>
       </c>
       <c r="L2">
-        <v>0.2072631578947368</v>
+        <v>0.249535192563081</v>
       </c>
       <c r="M2">
-        <v>6.28</v>
+        <v>5.97</v>
       </c>
       <c r="N2">
-        <v>0.06162904808635918</v>
+        <v>0.05085178875638841</v>
       </c>
       <c r="O2">
-        <v>0.318943626206196</v>
+        <v>0.3177221926556679</v>
       </c>
       <c r="P2">
-        <v>6.28</v>
+        <v>5.97</v>
       </c>
       <c r="Q2">
-        <v>0.06162904808635918</v>
+        <v>0.05085178875638841</v>
       </c>
       <c r="R2">
-        <v>0.318943626206196</v>
+        <v>0.3177221926556679</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.4</v>
+        <v>14.46</v>
       </c>
       <c r="V2">
-        <v>0.1020608439646712</v>
+        <v>0.1231686541737649</v>
+      </c>
+      <c r="W2">
+        <v>0.1941608594657375</v>
       </c>
       <c r="X2">
-        <v>0.1330936372347507</v>
+        <v>0.1358402034195225</v>
+      </c>
+      <c r="Y2">
+        <v>0.05832065604621506</v>
       </c>
       <c r="Z2">
-        <v>2.553763440860215</v>
+        <v>1.029814004376368</v>
+      </c>
+      <c r="AA2">
+        <v>0.2224139327240482</v>
       </c>
       <c r="AB2">
-        <v>0.1330936372347507</v>
+        <v>0.1357817256074024</v>
+      </c>
+      <c r="AC2">
+        <v>0.08663220711664583</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AG2">
-        <v>-10.4</v>
+        <v>-14.192</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.002277594588163307</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.00373425482109018</v>
       </c>
       <c r="AJ2">
-        <v>-0.1136612021857924</v>
+        <v>-0.1375087202542438</v>
       </c>
       <c r="AK2">
-        <v>-0.2561576354679803</v>
+        <v>-0.2476443079500244</v>
       </c>
       <c r="AL2">
-        <v>0.059</v>
+        <v>0.199</v>
       </c>
       <c r="AM2">
-        <v>0.059</v>
+        <v>0.199</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.01295311744804253</v>
       </c>
       <c r="AO2">
-        <v>388.9830508474577</v>
+        <v>102.5628140703517</v>
       </c>
       <c r="AP2">
-        <v>-0.4461604461604461</v>
+        <v>-0.6859352344127597</v>
       </c>
       <c r="AQ2">
-        <v>388.9830508474577</v>
+        <v>102.5628140703517</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mohandes Insurance Company (CASE:MOIN)</t>
+          <t>Delta Insurance Company (CASE:DEIN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,47 +721,41 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.109</v>
-      </c>
-      <c r="E3">
-        <v>0.0491</v>
-      </c>
       <c r="G3">
-        <v>0.2143631436314363</v>
+        <v>0.3653395784543325</v>
       </c>
       <c r="H3">
-        <v>0.2143631436314363</v>
+        <v>0.3653395784543325</v>
       </c>
       <c r="I3">
-        <v>0.2100271002710027</v>
+        <v>0.3208430913348946</v>
       </c>
       <c r="J3">
-        <v>0.173681248555378</v>
+        <v>0.2609374232325052</v>
       </c>
       <c r="K3">
-        <v>6.69</v>
+        <v>11.7</v>
       </c>
       <c r="L3">
-        <v>0.1813008130081301</v>
+        <v>0.2740046838407494</v>
       </c>
       <c r="M3">
-        <v>2.91</v>
+        <v>4.26</v>
       </c>
       <c r="N3">
-        <v>0.05553435114503817</v>
+        <v>0.0922077922077922</v>
       </c>
       <c r="O3">
-        <v>0.4349775784753363</v>
+        <v>0.3641025641025641</v>
       </c>
       <c r="P3">
-        <v>2.91</v>
+        <v>4.26</v>
       </c>
       <c r="Q3">
-        <v>0.05553435114503817</v>
+        <v>0.0922077922077922</v>
       </c>
       <c r="R3">
-        <v>0.4349775784753363</v>
+        <v>0.3641025641025641</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,16 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.1846320346320346</v>
+      </c>
+      <c r="W3">
+        <v>0.2195121951219512</v>
       </c>
       <c r="X3">
-        <v>0.1330936372347507</v>
+        <v>0.1356988698852867</v>
+      </c>
+      <c r="Y3">
+        <v>0.08381332523666454</v>
+      </c>
+      <c r="Z3">
+        <v>1.150943396226415</v>
+      </c>
+      <c r="AA3">
+        <v>0.300324204097789</v>
       </c>
       <c r="AB3">
-        <v>0.1330936372347507</v>
+        <v>0.1356988698852867</v>
+      </c>
+      <c r="AC3">
+        <v>0.1646253342125024</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -779,31 +800,37 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.2264401380408813</v>
+      </c>
+      <c r="AK3">
+        <v>-0.2659806672903025</v>
       </c>
       <c r="AL3">
-        <v>0.059</v>
+        <v>0.011</v>
       </c>
       <c r="AM3">
-        <v>0.059</v>
+        <v>0.011</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>131.3559322033898</v>
+        <v>1245.454545454545</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-0.6181159420289855</v>
       </c>
       <c r="AQ3">
-        <v>131.3559322033898</v>
+        <v>1245.454545454545</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Delta Insurance Company (CASE:DEIN)</t>
+          <t>Mohandes Insurance Company (CASE:MOIN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -822,41 +849,47 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.143</v>
+      </c>
+      <c r="E4">
+        <v>0.101</v>
+      </c>
       <c r="G4">
-        <v>0.2805507745266781</v>
+        <v>0.1779141104294479</v>
       </c>
       <c r="H4">
-        <v>0.2805507745266781</v>
+        <v>0.1779141104294479</v>
       </c>
       <c r="I4">
-        <v>0.261617900172117</v>
+        <v>0.2058282208588957</v>
       </c>
       <c r="J4">
-        <v>0.2185775359502526</v>
+        <v>0.1596632479091434</v>
       </c>
       <c r="K4">
-        <v>13</v>
+        <v>7.09</v>
       </c>
       <c r="L4">
-        <v>0.2237521514629948</v>
+        <v>0.2174846625766871</v>
       </c>
       <c r="M4">
-        <v>3.37</v>
+        <v>1.71</v>
       </c>
       <c r="N4">
-        <v>0.06808080808080809</v>
+        <v>0.02401685393258427</v>
       </c>
       <c r="O4">
-        <v>0.2592307692307693</v>
+        <v>0.2411847672778561</v>
       </c>
       <c r="P4">
-        <v>3.37</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>0.06808080808080809</v>
+        <v>0.02401685393258427</v>
       </c>
       <c r="R4">
-        <v>0.2592307692307693</v>
+        <v>0.2411847672778561</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -865,67 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>10.4</v>
+        <v>5.93</v>
       </c>
       <c r="V4">
-        <v>0.2101010101010101</v>
+        <v>0.08328651685393258</v>
       </c>
       <c r="W4">
-        <v>0.2490421455938697</v>
+        <v>0.1688095238095238</v>
       </c>
       <c r="X4">
-        <v>0.1330936372347507</v>
+        <v>0.1359815369537582</v>
       </c>
       <c r="Y4">
-        <v>0.115948508359119</v>
+        <v>0.03282798685576557</v>
       </c>
       <c r="Z4">
-        <v>1.561827956989247</v>
+        <v>0.9050527484730706</v>
       </c>
       <c r="AA4">
-        <v>0.3413805064169267</v>
+        <v>0.1445036613503075</v>
       </c>
       <c r="AB4">
-        <v>0.1330936372347507</v>
+        <v>0.1358645813295182</v>
       </c>
       <c r="AC4">
-        <v>0.208286869182176</v>
+        <v>0.008639080020789308</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AG4">
-        <v>-10.4</v>
+        <v>-5.662</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.003749930038618682</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.008598562628336756</v>
       </c>
       <c r="AJ4">
-        <v>-0.2659846547314578</v>
+        <v>-0.08639262717812567</v>
       </c>
       <c r="AK4">
-        <v>-0.2561576354679803</v>
+        <v>-0.2243442428084634</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.03889695210449928</v>
+      </c>
+      <c r="AO4">
+        <v>35.69148936170212</v>
       </c>
       <c r="AP4">
-        <v>-0.6753246753246753</v>
+        <v>-0.8217706821480407</v>
+      </c>
+      <c r="AQ4">
+        <v>35.69148936170212</v>
       </c>
     </row>
   </sheetData>
